--- a/stories/arbres/ATOM-SAN.HYG.003-05.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.003-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Luce est au parc avec papa. Son nez coule. Papa tend un mouchoir. Luce prend le mouchoir. Elle se mouche. Puis elle va à la poubelle du parc. Elle jette le mouchoir. Papa dit : mouchoir, puis poubelle. Luce répète : mouchoir. Poubelle.</t>
+          <t>Luce est au parc avec papa. Son nez coule. Papa tend un mouchoir. Luce prend le mouchoir. Elle se mouche. Puis elle va à la poubelle du parc. Elle jette le mouchoir. Mouchoir, puis poubelle. Luce répète : mouchoir. Poubelle.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Luce est au parc avec papa. Son nez coule. Papa tend un mouchoir. Luce prend le mouchoir. Elle se mouche. Puis elle va à la poubelle du parc. Elle jette le mouchoir.
+papa|Mouchoir, puis poubelle.
+narrateur|Luce répète : mouchoir. Poubelle.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1488,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Le nez de Luce coule. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1661,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Luce a pris un mouchoir. Elle l'a jeté à la poubelle.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1828,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Papa range un mouchoir propre. Luce donne la main.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1995,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2035,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.HYG.003-05.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.003-05.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1312,6 +1317,11 @@
 narrateur|Luce répète : mouchoir. Poubelle.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1495,6 +1505,7 @@
           <t>narrateur|Le nez de Luce coule. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1666,6 +1677,7 @@
           <t>narrateur|Luce a pris un mouchoir. Elle l'a jeté à la poubelle.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1845,7 @@
           <t>narrateur|Papa range un mouchoir propre. Luce donne la main.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2000,6 +2013,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2018,7 +2032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2042,6 +2056,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2243,6 +2271,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SAN.HYG.003-05.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.003-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Luce se mouche au parc</t>
+          <t>La feuille sèche</t>
         </is>
       </c>
     </row>
@@ -602,6 +602,11 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SAN.HYG.001</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -830,6 +835,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Une feuille sèche gratte le chemin. Le nez de Mila chatouille. Papa tend un mouchoir. Elle se mouche, puis jette le mouchoir à la poubelle verte.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1189,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Luce est au parc avec papa. Son nez coule. Papa tend un mouchoir. Luce prend le mouchoir. Elle se mouche. Puis elle va à la poubelle du parc. Elle jette le mouchoir. Mouchoir, puis poubelle. Luce répète : mouchoir. Poubelle.</t>
+          <t>Une feuille sèche gratte le chemin du parc. Elle fait un bruit de papier. Le banc en bois est tiède. Une fourmi monte sur le pied du banc. Derrière les arbres, le village est calme. Ça sent l'herbe coupée. Un oiseau tape trois coups, tout près. Papa a un manteau bleu. Une pointe blanche dépasse de la poche. En ce moment, Mila pousse la balançoire. La chaîne fait tic, tic. Son nez chatouille. Ça coule un peu. Papa. Mon nez. Viens près de moi. J'ai un mouchoir. Papa sort le mouchoir blanc. Il est doux, un peu froissé. Mila prend le mouchoir. Elle se mouche, tout doux. Atchoum. Le nez est plus libre. Bravo, Mila. Tu as pris le mouchoir. On va à la poubelle ? Oui, papa. La poubelle du parc est verte. Elle a un couvercle lisse. Mila ouvre un peu. Elle jette le mouchoir. Le couvercle retombe, toc. Mouchoir, puis poubelle. Mouchoir, puis poubelle. C'est du bon travail. Tu as fini de jeter le mouchoir ? Oui. On se lave les mains, après. La fontaine du parc chante. L'eau est froide. Mila frotte, puis essuie. Son nez est calme. Papa range un mouchoir propre. La feuille sèche part un peu plus loin.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,14 +1329,55 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Luce est au parc avec papa. Son nez coule. Papa tend un mouchoir. Luce prend le mouchoir. Elle se mouche. Puis elle va à la poubelle du parc. Elle jette le mouchoir.
+          <t>narrateur|Une feuille sèche gratte le chemin du parc.
+narrateur|Elle fait un bruit de papier.
+narrateur|Le banc en bois est tiède.
+narrateur|Une fourmi monte sur le pied du banc.
+narrateur|Derrière les arbres, le village est calme.
+narrateur|Ça sent l'herbe coupée.
+narrateur|Un oiseau tape trois coups, tout près.
+narrateur|Papa a un manteau bleu.
+narrateur|Une pointe blanche dépasse de la poche.
+narrateur|En ce moment, Mila pousse la balançoire.
+narrateur|La chaîne fait tic, tic.
+narrateur|Son nez chatouille.
+narrateur|Ça coule un peu.
+enfant-f|Papa.
+enfant-f|Mon nez.
+papa|Viens près de moi.
+papa|J'ai un mouchoir.
+narrateur|Papa sort le mouchoir blanc.
+narrateur|Il est doux, un peu froissé.
+narrateur|Mila prend le mouchoir.
+narrateur|Elle se mouche, tout doux.
+narrateur|Atchoum.
+narrateur|Le nez est plus libre.
+papa|Bravo, Mila.
+papa|Tu as pris le mouchoir.
+papa|On va à la poubelle ?
+enfant-f|Oui, papa.
+narrateur|La poubelle du parc est verte.
+narrateur|Elle a un couvercle lisse.
+narrateur|Mila ouvre un peu.
+narrateur|Elle jette le mouchoir.
+narrateur|Le couvercle retombe, toc.
 papa|Mouchoir, puis poubelle.
-narrateur|Luce répète : mouchoir. Poubelle.</t>
+enfant-f|Mouchoir, puis poubelle.
+papa|C'est du bon travail.
+papa|Tu as fini de jeter le mouchoir ?
+enfant-f|Oui.
+papa|On se lave les mains, après.
+narrateur|La fontaine du parc chante.
+narrateur|L'eau est froide.
+narrateur|Mila frotte, puis essuie.
+narrateur|Son nez est calme.
+narrateur|Papa range un mouchoir propre.
+narrateur|La feuille sèche part un peu plus loin.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>enfants_parc</t>
+          <t>enfants_parc,poubelle</t>
         </is>
       </c>
     </row>
@@ -1346,7 +1404,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Le nez de Luce coule. Que fait-elle ?</t>
+          <t>Le nez de Mila coule. Que prend-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1502,7 +1560,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Le nez de Luce coule. Que fait-elle ?</t>
+          <t>narrateur|Le nez de Mila coule.
+narrateur|Que prend-elle ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1530,7 +1589,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Luce a pris un mouchoir. Elle l'a jeté à la poubelle.</t>
+          <t>Mila a pris un mouchoir. Elle s'est mouchée, tout doux. Elle a jeté le mouchoir à la poubelle. Bravo. Tu as fait du bon travail. Le mouchoir, puis la poubelle. Oui, papa. La poubelle verte. La fourmi est encore sur le banc. Mila la regarde. Elle est toute petite. Tu as vu la fourmi ? Oui. Elle marche. Papa s'assoit un moment. Mila s'assoit près de lui. Le bois est encore tiède. Son nez est calme, maintenant.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1674,7 +1733,24 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Luce a pris un mouchoir. Elle l'a jeté à la poubelle.</t>
+          <t>narrateur|Mila a pris un mouchoir.
+narrateur|Elle s'est mouchée, tout doux.
+narrateur|Elle a jeté le mouchoir à la poubelle.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+papa|Le mouchoir, puis la poubelle.
+enfant-f|Oui, papa.
+enfant-f|La poubelle verte.
+narrateur|La fourmi est encore sur le banc.
+narrateur|Mila la regarde.
+narrateur|Elle est toute petite.
+papa|Tu as vu la fourmi ?
+enfant-f|Oui.
+enfant-f|Elle marche.
+narrateur|Papa s'assoit un moment.
+narrateur|Mila s'assoit près de lui.
+narrateur|Le bois est encore tiède.
+narrateur|Son nez est calme, maintenant.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1702,7 +1778,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Papa range un mouchoir propre. Luce donne la main.</t>
+          <t>Papa tend la main. Mila la prend. Elle est tiède. On rentre, tout doux ? Oui. Un mouchoir propre attend dans la poche. Au cas où. Merci, papa. Merci, Mila. Ils marchent sur le chemin. La feuille sèche n'est plus là. Un peu de sable reste dans une chaussure. Ça gratte. On l'enlève à la maison. D'accord. Le parc sent encore l'herbe. Mila donne un dernier regard au banc.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1842,7 +1918,23 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Papa range un mouchoir propre. Luce donne la main.</t>
+          <t>narrateur|Papa tend la main.
+narrateur|Mila la prend.
+narrateur|Elle est tiède.
+papa|On rentre, tout doux ?
+enfant-f|Oui.
+papa|Un mouchoir propre attend dans la poche.
+papa|Au cas où.
+enfant-f|Merci, papa.
+papa|Merci, Mila.
+narrateur|Ils marchent sur le chemin.
+narrateur|La feuille sèche n'est plus là.
+narrateur|Un peu de sable reste dans une chaussure.
+enfant-f|Ça gratte.
+papa|On l'enlève à la maison.
+enfant-f|D'accord.
+narrateur|Le parc sent encore l'herbe.
+narrateur|Mila donne un dernier regard au banc.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1870,7 +1962,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai pris un mouchoir. Puis la poubelle. Bravo. Tu as fait du bon travail. La feuille a gratté. On a joué. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2010,7 +2102,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai pris un mouchoir.
+enfant-f|Puis la poubelle.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+papa|La feuille a gratté.
+papa|On a joué.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2032,7 +2130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2070,6 +2168,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.HYG.003-05.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.003-05.xlsx
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une feuille sèche gratte le chemin du parc. Elle fait un bruit de papier. Le banc en bois est tiède. Une fourmi monte sur le pied du banc. Derrière les arbres, le village est calme. Ça sent l'herbe coupée. Un oiseau tape trois coups, tout près. Papa a un manteau bleu. Une pointe blanche dépasse de la poche. En ce moment, Mila pousse la balançoire. La chaîne fait tic, tic. Son nez chatouille. Ça coule un peu. Papa. Mon nez. Viens près de moi. J'ai un mouchoir. Papa sort le mouchoir blanc. Il est doux, un peu froissé. Mila prend le mouchoir. Elle se mouche, tout doux. Atchoum. Le nez est plus libre. Bravo, Mila. Tu as pris le mouchoir. On va à la poubelle ? Oui, papa. La poubelle du parc est verte. Elle a un couvercle lisse. Mila ouvre un peu. Elle jette le mouchoir. Le couvercle retombe, toc. Mouchoir, puis poubelle. Mouchoir, puis poubelle. C'est du bon travail. Tu as fini de jeter le mouchoir ? Oui. On se lave les mains, après. La fontaine du parc chante. L'eau est froide. Mila frotte, puis essuie. Son nez est calme. Papa range un mouchoir propre. La feuille sèche part un peu plus loin.</t>
+          <t>Une feuille sèche gratte le chemin du parc. Elle fait un bruit de papier. Le banc en bois est tiède. Une fourmi monte sur le pied du banc. Derrière les arbres, le village est calme. Ça sent l'herbe coupée. Un oiseau tape trois coups, tout près. Papa a un manteau bleu. Une pointe blanche dépasse de la poche. En ce moment, Mila pousse la balançoire. La chaîne fait tic, tic. Son nez chatouille. Ça coule un peu. Papa. Mon nez. Viens près de moi. J'ai un mouchoir. Papa sort le mouchoir blanc. Il est doux, un peu froissé. Mila prend le mouchoir. Elle se mouche, tout doux. Atchoum. Le nez est plus libre. Bravo, Mila. Tu as pris le mouchoir. On va à la poubelle ? Oui, papa. La poubelle du parc est verte. Elle a un couvercle lisse. Mila ouvre un peu. Elle jette le mouchoir. Le couvercle retombe, toc. Mouchoir, puis poubelle. Mouchoir, puis poubelle. Tu as fini de jeter le mouchoir ? Oui. On se lave les mains, après. La fontaine du parc chante. L'eau est froide. Mila frotte, puis essuie. Son nez est calme. Papa range un mouchoir propre. La feuille sèche part un peu plus loin.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Luce est au parc avec papa. Son nez coule. Papa tend un &lt;emphasis level="moderate"&gt;mouchoir&lt;/emphasis&gt;. Luce prend le mouchoir. Elle se mouche. Puis elle va à la poubelle du parc. Elle jette le mouchoir. Papa dit : mouchoir, puis poubelle. Luce répète : mouchoir. Poubelle.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une feuille sèche gratte le chemin du parc. Elle fait un bruit de papier. Le banc en bois est tiède. Une fourmi monte sur le pied du banc. Derrière les arbres, le village est calme. Ça sent l'herbe coupée. Un oiseau tape trois coups, tout près. Papa a un manteau bleu. Une pointe blanche dépasse de la poche. En ce moment, Mila pousse la balançoire. La chaîne fait tic, tic. Son nez chatouille. Ça coule un peu. Papa. Mon nez. Viens près de moi. J'ai un mouchoir. Papa sort le mouchoir blanc. Il est doux, un peu froissé. Mila prend le mouchoir. Elle se mouche, tout doux. Atchoum. Le nez est plus libre. Bravo, Mila. Tu as pris le mouchoir. On va à la poubelle ? Oui, papa. La poubelle du parc est verte. Elle a un couvercle lisse. Mila ouvre un peu. Elle jette le mouchoir. Le couvercle retombe, toc. Mouchoir, puis poubelle. Mouchoir, puis poubelle. Tu as fini de jeter le mouchoir ? Oui. On se lave les mains, après. La fontaine du parc chante. L'eau est froide. Mila frotte, puis essuie. Son nez est calme. Papa range un mouchoir propre. La feuille sèche part un peu plus loin.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1363,7 +1363,6 @@
 narrateur|Le couvercle retombe, toc.
 papa|Mouchoir, puis poubelle.
 enfant-f|Mouchoir, puis poubelle.
-papa|C'est du bon travail.
 papa|Tu as fini de jeter le mouchoir ?
 enfant-f|Oui.
 papa|On se lave les mains, après.
@@ -1409,7 +1408,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Le nez de Luce coule. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le nez de Mila coule. Que prend-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1564,7 +1563,6 @@
 narrateur|Que prend-elle ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1589,12 +1587,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Mila a pris un mouchoir. Elle s'est mouchée, tout doux. Elle a jeté le mouchoir à la poubelle. Bravo. Tu as fait du bon travail. Le mouchoir, puis la poubelle. Oui, papa. La poubelle verte. La fourmi est encore sur le banc. Mila la regarde. Elle est toute petite. Tu as vu la fourmi ? Oui. Elle marche. Papa s'assoit un moment. Mila s'assoit près de lui. Le bois est encore tiède. Son nez est calme, maintenant.</t>
+          <t>Mila a pris un mouchoir. Elle s'est mouchée, tout doux. Elle a jeté le mouchoir à la poubelle. Bravo. Le mouchoir, puis la poubelle. Oui, papa. La poubelle verte. La fourmi est encore sur le banc. Mila la regarde. Elle est toute petite. Tu as vu la fourmi ? Oui. Elle marche. Papa s'assoit un moment. Mila s'assoit près de lui. Le bois est encore tiède. Son nez est calme, maintenant.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Luce a pris un &lt;emphasis level="moderate"&gt;mouchoir&lt;/emphasis&gt;. Elle l'a jeté à la poubelle.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila a pris un mouchoir. Elle s'est mouchée, tout doux. Elle a jeté le mouchoir à la poubelle. Bravo. Le mouchoir, puis la poubelle. Oui, papa. La poubelle verte. La fourmi est encore sur le banc. Mila la regarde. Elle est toute petite. Tu as vu la fourmi ? Oui. Elle marche. Papa s'assoit un moment. Mila s'assoit près de lui. Le bois est encore tiède. Son nez est calme, maintenant.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1737,7 +1735,6 @@
 narrateur|Elle s'est mouchée, tout doux.
 narrateur|Elle a jeté le mouchoir à la poubelle.
 papa|Bravo.
-papa|Tu as fait du bon travail.
 papa|Le mouchoir, puis la poubelle.
 enfant-f|Oui, papa.
 enfant-f|La poubelle verte.
@@ -1753,7 +1750,6 @@
 narrateur|Son nez est calme, maintenant.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1783,7 +1779,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Papa range un &lt;emphasis level="moderate"&gt;mouchoir&lt;/emphasis&gt; propre. Luce donne la main.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Papa tend la main. Mila la prend. Elle est tiède. On rentre, tout doux ? Oui. Un mouchoir propre attend dans la poche. Au cas où. Merci, papa. Merci, Mila. Ils marchent sur le chemin. La feuille sèche n'est plus là. Un peu de sable reste dans une chaussure. Ça gratte. On l'enlève à la maison. D'accord. Le parc sent encore l'herbe. Mila donne un dernier regard au banc.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1937,7 +1933,6 @@
 narrateur|Mila donne un dernier regard au banc.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1962,12 +1957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai pris un mouchoir. Puis la poubelle. Bravo. Tu as fait du bon travail. La feuille a gratté. On a joué. L'histoire est finie.</t>
+          <t>J'ai pris un mouchoir. Puis la poubelle. Bravo. La feuille a gratté. On a joué.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai pris un mouchoir. Puis la poubelle. Bravo. La feuille a gratté. On a joué.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2105,13 +2100,10 @@
           <t>enfant-f|J'ai pris un mouchoir.
 enfant-f|Puis la poubelle.
 papa|Bravo.
-papa|Tu as fait du bon travail.
 papa|La feuille a gratté.
-papa|On a joué.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+papa|On a joué.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2130,7 +2122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2175,6 +2167,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.HYG.003-05.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.003-05.xlsx
@@ -688,7 +688,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Luce, papa</t>
+          <t>Mila, papa</t>
         </is>
       </c>
     </row>
